--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-18.xlsx
@@ -760,7 +760,7 @@
         <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
         <v>2.96</v>
@@ -772,16 +772,16 @@
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.26</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
@@ -790,16 +790,16 @@
         <v>2.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
         <v>2.56</v>
@@ -820,10 +820,10 @@
         <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
@@ -832,7 +832,7 @@
         <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
         <v>18.5</v>
@@ -841,7 +841,7 @@
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI2" t="n">
         <v>34</v>
@@ -859,10 +859,10 @@
         <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AP2" t="n">
         <v>21</v>
@@ -910,17 +910,17 @@
         <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>2.82</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="I3" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,22 +975,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="O3" t="n">
         <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -999,10 +999,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>3.55</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="I4" t="n">
         <v>2.24</v>
@@ -1160,7 +1160,7 @@
         <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1172,22 +1172,22 @@
         <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
         <v>2.18</v>
@@ -1196,7 +1196,7 @@
         <v>1.81</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>1.55</v>
       </c>
       <c r="G5" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J5" t="n">
         <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
@@ -1366,37 +1366,37 @@
         <v>5.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
         <v>2.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R5" t="n">
         <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
         <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="X5" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y5" t="n">
         <v>30</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>32</v>
       </c>
       <c r="Z5" t="n">
         <v>60</v>
@@ -1405,46 +1405,46 @@
         <v>160</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
         <v>13</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
         <v>18</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
@@ -1453,10 +1453,10 @@
         <v>19.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
         <v>19.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
         <v>13.5</v>
@@ -1492,17 +1492,17 @@
         <v>19.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
         <v>5.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="n">
         <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>4.3</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
         <v>1.93</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2545,10 +2545,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2560,7 +2560,7 @@
         <v>17</v>
       </c>
       <c r="Y11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z11" t="n">
         <v>36</v>
@@ -2599,7 +2599,7 @@
         <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
         <v>120</v>
@@ -2608,13 +2608,13 @@
         <v>17</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
         <v>4.9</v>
@@ -2623,34 +2623,34 @@
         <v>4.8</v>
       </c>
       <c r="AT11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU11" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU11" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
         <v>4.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
         <v>4.7</v>
       </c>
       <c r="BB11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC11" t="n">
         <v>18</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>16.5</v>
       </c>
       <c r="BD11" t="n">
         <v>4.8</v>
@@ -2659,14 +2659,14 @@
         <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG11" t="n">
         <v>4.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
         <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
         <v>3.95</v>
@@ -2924,7 +2924,7 @@
         <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>1.75</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>2.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H16" t="n">
         <v>3.7</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="G18" t="n">
         <v>2.08</v>
@@ -3876,7 +3876,7 @@
         <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
         <v>2.04</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
         <v>2.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
         <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
         <v>13</v>
@@ -4163,19 +4163,19 @@
         <v>5.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS19" t="n">
         <v>10.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU19" t="n">
         <v>10</v>
@@ -4187,10 +4187,10 @@
         <v>10.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ19" t="n">
         <v>16</v>
@@ -4199,26 +4199,26 @@
         <v>20</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG19" t="n">
         <v>3.9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>4.3</v>
       </c>
       <c r="K20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G21" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H21" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>3.55</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
         <v>1.73</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G23" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J23" t="n">
         <v>3.65</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>1.96</v>
       </c>
       <c r="H24" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I24" t="n">
         <v>8</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>1.53</v>
       </c>
       <c r="G26" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="H26" t="n">
         <v>7</v>
@@ -5428,7 +5428,7 @@
         <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>4.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K27" t="n">
         <v>3.75</v>
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q27" t="n">
         <v>2.12</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G28" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="I28" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="J28" t="n">
         <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -5998,16 +5998,16 @@
         <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>2.54</v>
       </c>
       <c r="K29" t="n">
         <v>950</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -6192,16 +6192,16 @@
         <v>2.12</v>
       </c>
       <c r="G30" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H30" t="n">
         <v>3.25</v>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
         <v>4.2</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
         <v>1.58</v>
       </c>
       <c r="H31" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="I31" t="n">
         <v>40</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="G32" t="n">
         <v>1000</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H34" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="K34" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -6995,7 +6995,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q34" t="n">
         <v>1.99</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G35" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H35" t="n">
         <v>6.4</v>
       </c>
       <c r="I35" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="G38" t="n">
         <v>1.76</v>
       </c>
       <c r="H38" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I38" t="n">
         <v>6.4</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G39" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H39" t="n">
         <v>2.82</v>
@@ -7947,10 +7947,10 @@
         <v>3.05</v>
       </c>
       <c r="J39" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -7965,10 +7965,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>2.38</v>
       </c>
       <c r="G41" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H41" t="n">
         <v>3.05</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
         <v>1.46</v>
       </c>
       <c r="P42" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q42" t="n">
         <v>2.38</v>
@@ -8646,7 +8646,7 @@
         <v>15.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AX42" t="n">
         <v>12</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="G43" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="I43" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="J43" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K43" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8741,10 +8741,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
         <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R44" t="n">
         <v>1.47</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -9102,13 +9102,13 @@
         <v>1.47</v>
       </c>
       <c r="G45" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H45" t="n">
         <v>7.2</v>
       </c>
       <c r="I45" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
         <v>5.2</v>
@@ -9126,19 +9126,19 @@
         <v>6.8</v>
       </c>
       <c r="O45" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P45" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q45" t="n">
         <v>1.49</v>
       </c>
       <c r="R45" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S45" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T45" t="n">
         <v>1.7</v>
@@ -9162,7 +9162,7 @@
         <v>75</v>
       </c>
       <c r="AA45" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB45" t="n">
         <v>13.5</v>
@@ -9171,10 +9171,10 @@
         <v>12.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE45" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF45" t="n">
         <v>12</v>
@@ -9186,7 +9186,7 @@
         <v>21</v>
       </c>
       <c r="AI45" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="n">
         <v>14</v>
@@ -9195,22 +9195,22 @@
         <v>14</v>
       </c>
       <c r="AL45" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN45" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO45" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP45" t="n">
         <v>26</v>
       </c>
       <c r="AQ45" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AR45" t="n">
         <v>32</v>
@@ -9252,17 +9252,17 @@
         <v>22</v>
       </c>
       <c r="BE45" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BF45" t="n">
         <v>4.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="G46" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H46" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="I46" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="J46" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -9323,10 +9323,10 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9556,7 @@
         <v>18</v>
       </c>
       <c r="AC47" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD47" t="n">
         <v>13</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -10263,19 +10263,19 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="H51" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J51" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="K51" t="n">
         <v>3.25</v>
@@ -10293,10 +10293,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G52" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H52" t="n">
         <v>4.8</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G53" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H53" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="I53" t="n">
         <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K53" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q53" t="n">
         <v>1.46</v>
@@ -10693,10 +10693,10 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U53" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -10753,7 +10753,7 @@
         <v>1000</v>
       </c>
       <c r="AN53" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO53" t="n">
         <v>1000</v>
@@ -10771,22 +10771,22 @@
         <v>4.9</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU53" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV53" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW53" t="n">
         <v>4.7</v>
       </c>
       <c r="AX53" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY53" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ53" t="n">
         <v>4</v>
@@ -10807,14 +10807,14 @@
         <v>4.8</v>
       </c>
       <c r="BF53" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG53" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -10845,19 +10845,19 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="G54" t="n">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="H54" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="I54" t="n">
         <v>1000</v>
       </c>
       <c r="J54" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="K54" t="n">
         <v>1000</v>
@@ -10878,7 +10878,7 @@
         <v>1.01</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -11233,19 +11233,19 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="G56" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H56" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="I56" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J56" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="K56" t="n">
         <v>1000</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -11433,13 +11433,13 @@
         <v>2.24</v>
       </c>
       <c r="H57" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="I57" t="n">
         <v>4.6</v>
       </c>
       <c r="J57" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K57" t="n">
         <v>4.1</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
         <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R59" t="n">
         <v>1.5</v>
@@ -11902,22 +11902,22 @@
         <v>20</v>
       </c>
       <c r="AI59" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ59" t="n">
         <v>130</v>
       </c>
       <c r="AK59" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL59" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM59" t="n">
         <v>100</v>
       </c>
       <c r="AN59" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO59" t="n">
         <v>9.199999999999999</v>
@@ -11959,26 +11959,26 @@
         <v>22</v>
       </c>
       <c r="BB59" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC59" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD59" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE59" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF59" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BG59" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -12009,19 +12009,19 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G60" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H60" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I60" t="n">
         <v>3.5</v>
       </c>
       <c r="J60" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K60" t="n">
         <v>3.5</v>
@@ -12039,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -12203,19 +12203,19 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G61" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H61" t="n">
         <v>3</v>
       </c>
       <c r="I61" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J61" t="n">
         <v>3.35</v>
-      </c>
-      <c r="J61" t="n">
-        <v>3.4</v>
       </c>
       <c r="K61" t="n">
         <v>3.8</v>
@@ -12236,7 +12236,7 @@
         <v>1.92</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -12397,10 +12397,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G62" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H62" t="n">
         <v>6.2</v>
@@ -12409,10 +12409,10 @@
         <v>7.4</v>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K62" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -12788,13 +12788,13 @@
         <v>1.87</v>
       </c>
       <c r="G64" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H64" t="n">
         <v>4.3</v>
       </c>
       <c r="I64" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>3.6</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -13185,7 +13185,7 @@
         <v>3.2</v>
       </c>
       <c r="J66" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K66" t="n">
         <v>5.6</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -13376,13 +13376,13 @@
         <v>7.4</v>
       </c>
       <c r="I67" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J67" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K67" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
         <v>3.2</v>
       </c>
       <c r="H68" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="I68" t="n">
         <v>4.7</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="G69" t="n">
         <v>3.45</v>
@@ -13770,7 +13770,7 @@
         <v>2.92</v>
       </c>
       <c r="K69" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -13788,7 +13788,7 @@
         <v>1.66</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -13952,16 +13952,16 @@
         <v>1.76</v>
       </c>
       <c r="G70" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H70" t="n">
         <v>5.1</v>
       </c>
       <c r="I70" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J70" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K70" t="n">
         <v>4.2</v>
@@ -13979,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q70" t="n">
         <v>2.06</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
         <v>32</v>
       </c>
       <c r="AG71" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH71" t="n">
         <v>14.5</v>
@@ -14248,7 +14248,7 @@
         <v>19.5</v>
       </c>
       <c r="AO71" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP71" t="n">
         <v>21</v>
@@ -14275,7 +14275,7 @@
         <v>16</v>
       </c>
       <c r="AX71" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AY71" t="n">
         <v>14</v>
@@ -14290,7 +14290,7 @@
         <v>30</v>
       </c>
       <c r="BC71" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BD71" t="n">
         <v>28</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -14343,13 +14343,13 @@
         <v>2.84</v>
       </c>
       <c r="H72" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="J72" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K72" t="n">
         <v>3.75</v>
@@ -14367,10 +14367,10 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -14767,7 +14767,7 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U74" t="n">
         <v>2.28</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -15006,7 +15006,7 @@
         <v>22</v>
       </c>
       <c r="AI75" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ75" t="n">
         <v>60</v>
@@ -15021,7 +15021,7 @@
         <v>1000</v>
       </c>
       <c r="AN75" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO75" t="n">
         <v>44</v>
@@ -15036,7 +15036,7 @@
         <v>15</v>
       </c>
       <c r="AS75" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT75" t="n">
         <v>8.6</v>
@@ -15072,17 +15072,17 @@
         <v>50</v>
       </c>
       <c r="BE75" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF75" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG75" t="n">
         <v>30</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -15116,16 +15116,16 @@
         <v>3.9</v>
       </c>
       <c r="G76" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H76" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I76" t="n">
         <v>2.24</v>
       </c>
       <c r="J76" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K76" t="n">
         <v>3.35</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
         <v>5.1</v>
       </c>
       <c r="K78" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -15534,7 +15534,7 @@
         <v>2.42</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -15695,22 +15695,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="G79" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H79" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I79" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J79" t="n">
         <v>3.55</v>
       </c>
       <c r="K79" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -15725,10 +15725,10 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -16292,7 +16292,7 @@
         <v>3.2</v>
       </c>
       <c r="K82" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -16310,7 +16310,7 @@
         <v>1.76</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -16665,22 +16665,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H84" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I84" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J84" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K84" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -16859,13 +16859,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G85" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H85" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="I85" t="n">
         <v>2.26</v>
@@ -16874,7 +16874,7 @@
         <v>3.3</v>
       </c>
       <c r="K85" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -16889,7 +16889,7 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q85" t="n">
         <v>2.14</v>
@@ -16913,7 +16913,7 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y85" t="n">
         <v>10.5</v>
@@ -17000,29 +17000,29 @@
         <v>17</v>
       </c>
       <c r="BA85" t="n">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BB85" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC85" t="n">
-        <v>4.1</v>
+        <v>38</v>
       </c>
       <c r="BD85" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE85" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF85" t="n">
-        <v>4.2</v>
+        <v>44</v>
       </c>
       <c r="BG85" t="n">
         <v>14</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -17065,7 +17065,7 @@
         <v>3.6</v>
       </c>
       <c r="J86" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K86" t="n">
         <v>3.85</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -17441,22 +17441,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="H88" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="I88" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="J88" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K88" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -17471,10 +17471,10 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17641,7 @@
         <v>2.68</v>
       </c>
       <c r="H89" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I89" t="n">
         <v>2.86</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -17829,16 +17829,16 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G90" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H90" t="n">
         <v>3.05</v>
       </c>
       <c r="I90" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J90" t="n">
         <v>3.85</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -18220,19 +18220,19 @@
         <v>2.08</v>
       </c>
       <c r="G92" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H92" t="n">
         <v>3.45</v>
       </c>
       <c r="I92" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J92" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -18247,7 +18247,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q92" t="n">
         <v>1.92</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -18435,7 +18435,7 @@
         <v>1.08</v>
       </c>
       <c r="N93" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O93" t="n">
         <v>1.35</v>
@@ -18450,7 +18450,7 @@
         <v>1.34</v>
       </c>
       <c r="S93" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T93" t="n">
         <v>1.82</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -18635,10 +18635,10 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -18802,19 +18802,19 @@
         <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H95" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I95" t="n">
         <v>5.2</v>
       </c>
       <c r="J95" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K95" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19017,7 @@
         <v>1.06</v>
       </c>
       <c r="N96" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O96" t="n">
         <v>1.28</v>
@@ -19035,10 +19035,10 @@
         <v>3.15</v>
       </c>
       <c r="T96" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U96" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -19053,7 +19053,7 @@
         <v>23</v>
       </c>
       <c r="Z96" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA96" t="n">
         <v>250</v>
@@ -19110,7 +19110,7 @@
         <v>10</v>
       </c>
       <c r="AS96" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT96" t="n">
         <v>7.8</v>
@@ -19122,7 +19122,7 @@
         <v>22</v>
       </c>
       <c r="AW96" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX96" t="n">
         <v>8.4</v>
@@ -19134,7 +19134,7 @@
         <v>18.5</v>
       </c>
       <c r="BA96" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB96" t="n">
         <v>13</v>
@@ -19143,7 +19143,7 @@
         <v>14.5</v>
       </c>
       <c r="BD96" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE96" t="n">
         <v>11</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -19193,7 +19193,7 @@
         <v>2.28</v>
       </c>
       <c r="H97" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I97" t="n">
         <v>4.2</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -19381,22 +19381,22 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="G98" t="n">
         <v>3.1</v>
       </c>
       <c r="H98" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I98" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J98" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K98" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -19590,7 +19590,7 @@
         <v>4.4</v>
       </c>
       <c r="K99" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -19769,19 +19769,19 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="G100" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="H100" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I100" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J100" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="K100" t="n">
         <v>1000</v>
@@ -19799,10 +19799,10 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="Q100" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -19963,19 +19963,19 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="G101" t="n">
         <v>1000</v>
       </c>
       <c r="H101" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="I101" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="J101" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K101" t="n">
         <v>950</v>
@@ -19993,10 +19993,10 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -20157,22 +20157,22 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="G102" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H102" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I102" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J102" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="K102" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -20187,10 +20187,10 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -20351,19 +20351,19 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="G103" t="n">
-        <v>1000</v>
+        <v>1.61</v>
       </c>
       <c r="H103" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="I103" t="n">
         <v>1000</v>
       </c>
       <c r="J103" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="K103" t="n">
         <v>1000</v>
@@ -20381,10 +20381,10 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>1.05</v>
+        <v>1.82</v>
       </c>
       <c r="Q103" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -20545,88 +20545,88 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="G104" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="H104" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="I104" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J104" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="K104" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L104" t="n">
         <v>1.01</v>
       </c>
       <c r="M104" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N104" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O104" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P104" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="R104" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="S104" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T104" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U104" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V104" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W104" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="X104" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y104" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z104" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA104" t="n">
         <v>1000</v>
       </c>
       <c r="AB104" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC104" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD104" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE104" t="n">
         <v>1000</v>
       </c>
       <c r="AF104" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG104" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH104" t="n">
         <v>1000</v>
@@ -20635,19 +20635,19 @@
         <v>1000</v>
       </c>
       <c r="AJ104" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK104" t="n">
         <v>1000</v>
       </c>
       <c r="AL104" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM104" t="n">
         <v>1000</v>
       </c>
       <c r="AN104" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO104" t="n">
         <v>1000</v>
@@ -20701,14 +20701,14 @@
         <v>1.03</v>
       </c>
       <c r="BF104" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG104" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -20739,22 +20739,22 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="G105" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H105" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="I105" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="K105" t="n">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L105" t="n">
         <v>1.01</v>
@@ -20763,22 +20763,22 @@
         <v>1.01</v>
       </c>
       <c r="N105" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="O105" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="P105" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q105" t="n">
-        <v>1.41</v>
+        <v>2.12</v>
       </c>
       <c r="R105" t="n">
         <v>1.13</v>
       </c>
       <c r="S105" t="n">
-        <v>1.41</v>
+        <v>2.12</v>
       </c>
       <c r="T105" t="n">
         <v>1.01</v>
@@ -20787,10 +20787,10 @@
         <v>1.01</v>
       </c>
       <c r="V105" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W105" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X105" t="n">
         <v>1000</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -20933,109 +20933,109 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="G106" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H106" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="I106" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J106" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="K106" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L106" t="n">
         <v>1.01</v>
       </c>
       <c r="M106" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N106" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="O106" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="P106" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="R106" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S106" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="T106" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U106" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V106" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W106" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X106" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y106" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z106" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA106" t="n">
         <v>1000</v>
       </c>
       <c r="AB106" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC106" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD106" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE106" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF106" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG106" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH106" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI106" t="n">
         <v>1000</v>
       </c>
       <c r="AJ106" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK106" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL106" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM106" t="n">
         <v>1000</v>
       </c>
       <c r="AN106" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO106" t="n">
         <v>1000</v>
@@ -21089,14 +21089,14 @@
         <v>1.03</v>
       </c>
       <c r="BF106" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG106" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -21321,22 +21321,22 @@
         </is>
       </c>
       <c r="F108" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G108" t="n">
         <v>1.42</v>
-      </c>
-      <c r="G108" t="n">
-        <v>1.52</v>
       </c>
       <c r="H108" t="n">
         <v>7.8</v>
       </c>
       <c r="I108" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="J108" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="K108" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -21351,10 +21351,10 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -21515,16 +21515,16 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="G109" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="H109" t="n">
         <v>6</v>
       </c>
       <c r="I109" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J109" t="n">
         <v>3.5</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G110" t="n">
         <v>1.47</v>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -21918,7 +21918,7 @@
         <v>3.25</v>
       </c>
       <c r="K111" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="L111" t="n">
         <v>1.01</v>
@@ -21927,16 +21927,16 @@
         <v>1.01</v>
       </c>
       <c r="N111" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="O111" t="n">
         <v>1.26</v>
       </c>
       <c r="P111" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R111" t="n">
         <v>1.36</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -22291,22 +22291,22 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G113" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="H113" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I113" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J113" t="n">
         <v>4</v>
       </c>
       <c r="K113" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -22324,7 +22324,7 @@
         <v>1.24</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -22679,7 +22679,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G115" t="n">
         <v>1.98</v>
@@ -22688,10 +22688,10 @@
         <v>4.3</v>
       </c>
       <c r="I115" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J115" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K115" t="n">
         <v>4</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -22903,7 +22903,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q116" t="n">
         <v>1.86</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
         <v>2.96</v>
       </c>
       <c r="G117" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H117" t="n">
         <v>2.34</v>
@@ -23082,7 +23082,7 @@
         <v>3.5</v>
       </c>
       <c r="K117" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -23100,7 +23100,7 @@
         <v>1.07</v>
       </c>
       <c r="Q117" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -23261,16 +23261,16 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G118" t="n">
         <v>2.7</v>
       </c>
       <c r="H118" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I118" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J118" t="n">
         <v>3.85</v>
@@ -23294,7 +23294,7 @@
         <v>2.44</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
